--- a/testes/perfis_exemplo/matriz_curricular.xlsx
+++ b/testes/perfis_exemplo/matriz_curricular.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equivalencias" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nucleos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Areas" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temas" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudos" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competencias" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perfil" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equivalencias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nucleos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Areas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competencias" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,245 +420,534 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>codigo</t>
+          <t>chave</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nome</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tipo</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>periodo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ativo</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>obrigatorio</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>cht</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>chp</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>chd</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>che</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>tot</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>observacoes</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>pre_requisitos</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>correquisitos</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>perfil.id</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fundamentos de Teste</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>disciplina</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>30</v>
+          <t>perfil_minimo</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>perfil.nome</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Teste Avançado</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>disciplina</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>30</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>D1</t>
+          <t>Perfil Mínimo de Testes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EXT1</t>
+          <t>perfil.status</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Extensão de Teste</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>extensao</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" t="n">
-        <v>15</v>
+          <t>vigente</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OPT1</t>
+          <t>perfil.versao</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optativa de Teste</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>carga_optativa</t>
-        </is>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+          <t>teste-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>perfil.descricao</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Perfil autocontido e mínimo, usado apenas pelos testes automatizados (Seção 20/21) — não é dado real de produção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>perfil.extends</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>curso.nome</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Curso de Teste</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>curso.nome_curto</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>curso.sigla</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TST</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>curso.grau</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tecnólogo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>curso.modalidade</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>curso.turno</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Integral</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>curso.regime_academico</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>curso.numero_periodos</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>curso.campus</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Campus de Teste</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>curso.municipio</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cidade de Teste</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>curso.estado</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>instituicao.nome</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Instituição de Teste</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>instituicao.sigla</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>instituicao.unidade_academica</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Unidade de Teste</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>curriculo.carga_horaria_total</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>curriculo.carga_obrigatoria</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>curriculo.carga_optativa_minima</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>30</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>30</v>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>curriculo.carga_extensao</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>curriculo.carga_aac</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>curriculo.carga_estagio</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>curriculo.carga_tcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>curriculo.percentual_minimo_extensao</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>curriculo.percentual_maximo_ead</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>curriculo.carga_horaria_maxima_periodo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>curriculo.periodo_minimo_tcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>curriculo.periodo_minimo_estagio</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>arquivos.textos</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>textos</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>arquivos.fichas</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>fichas</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>arquivos.figuras</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>figuras</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>arquivos.anexos</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>anexos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>arquivos.frontmatter</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>frontmatter</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>arquivos.overrides</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>overrides</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>geracao.template</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>padrao</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>geracao.anexar_fichas</t>
+        </is>
+      </c>
+      <c r="B41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>geracao.anexar_resolucoes</t>
+        </is>
+      </c>
+      <c r="B42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>geracao.gerar_fluxo_curricular</t>
+        </is>
+      </c>
+      <c r="B43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>geracao.gerar_representacao_grafica</t>
+        </is>
+      </c>
+      <c r="B44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>geracao.gerar_relatorio_validacao</t>
+        </is>
+      </c>
+      <c r="B45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>geracao.compilar_pdf</t>
+        </is>
+      </c>
+      <c r="B46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>geracao.interromper_em_erro</t>
+        </is>
+      </c>
+      <c r="B47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>saida.nome_base</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PPC_perfil_minimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>saida.gerar_corpo</t>
+        </is>
+      </c>
+      <c r="B49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>saida.gerar_completo</t>
+        </is>
+      </c>
+      <c r="B50" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -671,24 +961,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>codigo_origem</t>
+          <t>codigo</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>codigo_destino</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>observacao</t>
-        </is>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>periodo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ativo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>obrigatorio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>cht</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>chp</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>chd</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>che</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tot</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>observacoes</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>pre_requisitos</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>correquisitos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fundamentos de Teste</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>disciplina</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Teste Avançado</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>disciplina</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>30</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EXT1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Extensão de Teste</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>extensao</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OPT1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Optativa de Teste</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>carga_optativa</t>
+        </is>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -702,96 +1213,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>codigo_origem</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>nome</t>
+          <t>codigo_destino</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>descricao</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>componentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BASICO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Núcleo Básico de Teste</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TECNOLOGICO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Núcleo Tecnológico de Teste</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HUMANISTICO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Núcleo Humanístico de Teste</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>EXT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OPTATIVO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Núcleo Optativo de Teste</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>OPT1</t>
+          <t>observacao</t>
         </is>
       </c>
     </row>
@@ -806,7 +1244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,12 +1272,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MATEMATICA</t>
+          <t>BASICO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Matemática</t>
+          <t>Núcleo Básico de Teste</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -851,34 +1289,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>COMPUTACAO</t>
+          <t>TECNOLOGICO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Computação</t>
+          <t>Núcleo Tecnológico de Teste</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D2|OPT1</t>
+          <t>D2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EXTENSAO</t>
+          <t>HUMANISTICO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Extensão</t>
+          <t>Núcleo Humanístico de Teste</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>EXT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>OPTATIVO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Núcleo Optativo de Teste</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OPT1</t>
         </is>
       </c>
     </row>
@@ -893,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,17 +1369,58 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>fonte_normativa</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>componentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MATEMATICA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Matemática</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>COMPUTACAO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Computação</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>D2|OPT1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EXTENSAO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Extensão</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EXT1</t>
         </is>
       </c>
     </row>
@@ -939,7 +1435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,20 +1446,25 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>descricao</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>obrigatorio</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>fonte</t>
+          <t>fonte_normativa</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>componentes</t>
         </is>
@@ -980,6 +1481,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>descricao</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>obrigatorio</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fonte</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>componentes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1024,7 +1566,6 @@
       <c r="C2" t="b">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>D2</t>

--- a/testes/perfis_exemplo/matriz_curricular.xlsx
+++ b/testes/perfis_exemplo/matriz_curricular.xlsx
@@ -15,6 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temas" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteudos" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Competencias" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Autoridades" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comissao" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -815,43 +817,41 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>arquivos.frontmatter</t>
+          <t>arquivos.overrides</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>frontmatter</t>
+          <t>overrides</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>arquivos.overrides</t>
+          <t>geracao.template</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>overrides</t>
+          <t>padrao</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>geracao.template</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>padrao</t>
-        </is>
+          <t>geracao.anexar_fichas</t>
+        </is>
+      </c>
+      <c r="B40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>geracao.anexar_fichas</t>
+          <t>geracao.anexar_resolucoes</t>
         </is>
       </c>
       <c r="B41" t="b">
@@ -861,7 +861,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>geracao.anexar_resolucoes</t>
+          <t>geracao.gerar_fluxo_curricular</t>
         </is>
       </c>
       <c r="B42" t="b">
@@ -871,7 +871,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>geracao.gerar_fluxo_curricular</t>
+          <t>geracao.gerar_representacao_grafica</t>
         </is>
       </c>
       <c r="B43" t="b">
@@ -881,7 +881,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>geracao.gerar_representacao_grafica</t>
+          <t>geracao.gerar_relatorio_validacao</t>
         </is>
       </c>
       <c r="B44" t="b">
@@ -891,7 +891,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>geracao.gerar_relatorio_validacao</t>
+          <t>geracao.compilar_pdf</t>
         </is>
       </c>
       <c r="B45" t="b">
@@ -901,7 +901,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>geracao.compilar_pdf</t>
+          <t>geracao.interromper_em_erro</t>
         </is>
       </c>
       <c r="B46" t="b">
@@ -911,43 +911,54 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>geracao.interromper_em_erro</t>
-        </is>
-      </c>
-      <c r="B47" t="b">
-        <v>1</v>
+          <t>saida.nome_base</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PPC_perfil_minimo</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>saida.nome_base</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>PPC_perfil_minimo</t>
-        </is>
+          <t>saida.gerar_corpo</t>
+        </is>
+      </c>
+      <c r="B48" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>saida.gerar_corpo</t>
+          <t>saida.gerar_completo</t>
         </is>
       </c>
       <c r="B49" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>saida.gerar_completo</t>
-        </is>
-      </c>
-      <c r="B50" t="b">
-        <v>1</v>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>membro</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1575,4 +1586,35 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cargo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>nome</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>observacoes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/testes/perfis_exemplo/matriz_curricular.xlsx
+++ b/testes/perfis_exemplo/matriz_curricular.xlsx
@@ -972,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,45 +1003,40 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>obrigatorio</t>
+          <t>cht</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>cht</t>
+          <t>chp</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>chp</t>
+          <t>chd</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>chd</t>
+          <t>che</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>che</t>
+          <t>tot</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>tot</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>pre_requisitos</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
-        <is>
-          <t>pre_requisitos</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
         <is>
           <t>correquisitos</t>
         </is>
@@ -1069,11 +1064,11 @@
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
+      <c r="F2" t="n">
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1082,9 +1077,6 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1110,11 +1102,11 @@
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
+      <c r="F3" t="n">
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -1123,12 +1115,9 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
         <v>30</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
@@ -1156,8 +1145,8 @@
       <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
+      <c r="F4" t="n">
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1166,14 +1155,11 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
         <v>15</v>
       </c>
-      <c r="K4" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1194,11 +1180,11 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="b">
+      <c r="F5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>30</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1207,9 +1193,6 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
         <v>30</v>
       </c>
     </row>

--- a/testes/perfis_exemplo/matriz_curricular.xlsx
+++ b/testes/perfis_exemplo/matriz_curricular.xlsx
@@ -748,7 +748,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>curriculo.carga_horaria_maxima_periodo</t>
+          <t>curriculo.carga_horaria_presencial_maxima_periodo</t>
         </is>
       </c>
     </row>

--- a/testes/perfis_exemplo/matriz_curricular.xlsx
+++ b/testes/perfis_exemplo/matriz_curricular.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,155 +693,155 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>curriculo.carga_optativa_minima</t>
+          <t>curriculo.carga_extensao</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>curriculo.carga_extensao</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>15</v>
+          <t>curriculo.carga_aac</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>curriculo.carga_aac</t>
+          <t>curriculo.carga_estagio</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>curriculo.carga_estagio</t>
+          <t>curriculo.carga_tcc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>curriculo.carga_tcc</t>
+          <t>curriculo.percentual_minimo_extensao</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>curriculo.percentual_minimo_extensao</t>
+          <t>curriculo.percentual_maximo_ead</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>curriculo.percentual_maximo_ead</t>
+          <t>curriculo.carga_horaria_presencial_maxima_periodo</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>curriculo.carga_horaria_presencial_maxima_periodo</t>
+          <t>curriculo.periodo_minimo_tcc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>curriculo.periodo_minimo_tcc</t>
+          <t>curriculo.periodo_minimo_estagio</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>curriculo.periodo_minimo_estagio</t>
+          <t>arquivos.textos</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>textos</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>arquivos.textos</t>
+          <t>arquivos.fichas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>textos</t>
+          <t>fichas</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>arquivos.fichas</t>
+          <t>arquivos.figuras</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>fichas</t>
+          <t>figuras</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>arquivos.figuras</t>
+          <t>arquivos.anexos</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>figuras</t>
+          <t>anexos</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>arquivos.anexos</t>
+          <t>arquivos.overrides</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>anexos</t>
+          <t>overrides</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>arquivos.overrides</t>
+          <t>geracao.template</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>overrides</t>
+          <t>padrao</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>geracao.template</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>padrao</t>
-        </is>
+          <t>geracao.anexar_fichas</t>
+        </is>
+      </c>
+      <c r="B39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>geracao.anexar_fichas</t>
+          <t>geracao.anexar_resolucoes</t>
         </is>
       </c>
       <c r="B40" t="b">
@@ -851,7 +851,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>geracao.anexar_resolucoes</t>
+          <t>geracao.gerar_fluxo_curricular</t>
         </is>
       </c>
       <c r="B41" t="b">
@@ -861,7 +861,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>geracao.gerar_fluxo_curricular</t>
+          <t>geracao.gerar_representacao_grafica</t>
         </is>
       </c>
       <c r="B42" t="b">
@@ -871,7 +871,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>geracao.gerar_representacao_grafica</t>
+          <t>geracao.gerar_relatorio_validacao</t>
         </is>
       </c>
       <c r="B43" t="b">
@@ -881,7 +881,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>geracao.gerar_relatorio_validacao</t>
+          <t>geracao.compilar_pdf</t>
         </is>
       </c>
       <c r="B44" t="b">
@@ -891,7 +891,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>geracao.compilar_pdf</t>
+          <t>geracao.interromper_em_erro</t>
         </is>
       </c>
       <c r="B45" t="b">
@@ -901,42 +901,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>geracao.interromper_em_erro</t>
-        </is>
-      </c>
-      <c r="B46" t="b">
-        <v>1</v>
+          <t>saida.nome_base</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PPC_perfil_minimo</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>saida.nome_base</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>PPC_perfil_minimo</t>
-        </is>
+          <t>saida.gerar_corpo</t>
+        </is>
+      </c>
+      <c r="B47" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>saida.gerar_corpo</t>
+          <t>saida.gerar_completo</t>
         </is>
       </c>
       <c r="B48" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>saida.gerar_completo</t>
-        </is>
-      </c>
-      <c r="B49" t="b">
         <v>1</v>
       </c>
     </row>
@@ -972,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1183,41 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MODOPT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MÓDULO OPTATIVO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>carga_optativa</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>30</v>
       </c>
     </row>
